--- a/SB3_tests/Cartpole/summary_metrics.xlsx
+++ b/SB3_tests/Cartpole/summary_metrics.xlsx
@@ -431,56 +431,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>env_noise</t>
+          <t>EnvNoise</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>run_noise</t>
+          <t>RunNoise</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_reward</t>
+          <t>Mean Reward</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_stabilisation_time_s</t>
+          <t>Mean Stabilisation Time</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_steady_state_offset_deg</t>
+          <t>Mean Steady-state offset</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_total_stable_time_s</t>
+          <t>Mean Total Stable Time</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State MAE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State RMSE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Oscillation (σ)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mean |Overshoot/Undershoot|</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mean IAE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Control Energy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>results_path</t>
         </is>
@@ -510,7 +546,25 @@
       <c r="G2" t="n">
         <v>4.67</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>plots\A2C\a2c_env_noise_0.000\a2c_noise_0.000\A2C_results.txt</t>
         </is>
@@ -540,7 +594,25 @@
       <c r="G3" t="n">
         <v>4.61</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="L3" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="M3" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>plots\A2C\a2c_env_noise_0.000\a2c_noise_0.001\A2C_results.txt</t>
         </is>
@@ -570,7 +642,25 @@
       <c r="G4" t="n">
         <v>4.69</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>plots\A2C\a2c_env_noise_0.000\a2c_noise_0.010\A2C_results.txt</t>
         </is>
@@ -600,7 +690,25 @@
       <c r="G5" t="n">
         <v>2.33</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="M5" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>plots\A2C\a2c_env_noise_0.000\a2c_noise_0.100\A2C_results.txt</t>
         </is>
@@ -619,20 +727,38 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>492.92</v>
+        <v>494.88</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3</v>
+        <v>0.43</v>
       </c>
       <c r="F6" t="n">
-        <v>6.21</v>
+        <v>3.84</v>
       </c>
       <c r="G6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>plots\A2C\a2c_env_noise_0.001\a2c\A2C_results.txt</t>
+        <v>4.67</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L6" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.001\a2c_noise_0.000\A2C_results.txt</t>
         </is>
       </c>
     </row>
@@ -643,26 +769,44 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D7" t="n">
-        <v>492.92</v>
+        <v>495.49</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3</v>
+        <v>0.49</v>
       </c>
       <c r="F7" t="n">
-        <v>6.21</v>
+        <v>-1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>plots\A2C\a2c_env_noise_0.010\a2c\A2C_results.txt</t>
+        <v>4.61</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="L7" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="M7" t="n">
+        <v>320.13</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.001\a2c_noise_0.001\A2C_results.txt</t>
         </is>
       </c>
     </row>
@@ -673,626 +817,4316 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1</v>
+        <v>0.001</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>492.43</v>
+        <v>495.85</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>0.41</v>
       </c>
       <c r="F8" t="n">
-        <v>7.14</v>
+        <v>-0.67</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>plots\A2C\a2c_env_noise_0.100\a2c\A2C_results.txt</t>
+        <v>4.69</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.001\a2c_noise_0.010\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DDPG</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D9" t="n">
-        <v>496.03</v>
+        <v>305.31</v>
       </c>
       <c r="E9" t="n">
-        <v>0.32</v>
+        <v>0.93</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-27.02</v>
       </c>
       <c r="G9" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.000\DDPG_results.txt</t>
+        <v>2.33</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="L9" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="M9" t="n">
+        <v>70.31</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.001\a2c_noise_0.100\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DDPG</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>494.56</v>
+        <v>494.81</v>
       </c>
       <c r="E10" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="F10" t="n">
-        <v>1.48</v>
+        <v>3.96</v>
       </c>
       <c r="G10" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.001\DDPG_results.txt</t>
+        <v>4.64</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="L10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.010\a2c_noise_0.000\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DDPG</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="D11" t="n">
-        <v>301.17</v>
+        <v>495.49</v>
       </c>
       <c r="E11" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-28.04</v>
+        <v>-1.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.010\DDPG_results.txt</t>
+        <v>4.61</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L11" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="M11" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.010\a2c_noise_0.001\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DDPG</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D12" t="n">
-        <v>491.92</v>
+        <v>495.86</v>
       </c>
       <c r="E12" t="n">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.54</v>
+        <v>-0.59</v>
       </c>
       <c r="G12" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.100\DDPG_results.txt</t>
+        <v>4.69</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="M12" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.010\a2c_noise_0.010\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DQN</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>465.72</v>
+        <v>305.23</v>
       </c>
       <c r="E13" t="n">
-        <v>3.09</v>
+        <v>1.01</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.25</v>
+        <v>-26.78</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.000\DQN_results.txt</t>
+        <v>2.31</v>
+      </c>
+      <c r="H13" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="I13" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="K13" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.010\a2c_noise_0.100\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DQN</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>478.08</v>
+        <v>493.58</v>
       </c>
       <c r="E14" t="n">
-        <v>3.09</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.24</v>
+        <v>6.01</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.001\DQN_results.txt</t>
+        <v>2.32</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="L14" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="M14" t="n">
+        <v>106.31</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.100\a2c_noise_0.000\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DQN</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="D15" t="n">
-        <v>473.33</v>
+        <v>495.24</v>
       </c>
       <c r="E15" t="n">
-        <v>3.09</v>
+        <v>2.78</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.57</v>
+        <v>-1.38</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.010\DQN_results.txt</t>
+        <v>3.06</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.100\a2c_noise_0.001\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DQN</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D16" t="n">
-        <v>301.27</v>
+        <v>495.59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.24</v>
+        <v>3.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-31.39</v>
+        <v>1.96</v>
       </c>
       <c r="G16" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.100\DQN_results.txt</t>
+        <v>3.12</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.100\a2c_noise_0.010\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>305.26</v>
+        <v>305.19</v>
       </c>
       <c r="E17" t="n">
-        <v>0.67</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.16</v>
+        <v>-29.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.000\PPO_results.txt</t>
+        <v>1.53</v>
+      </c>
+      <c r="H17" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="I17" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="K17" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="L17" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.03</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.100\a2c_noise_0.100\A2C_results.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>112.03</v>
+        <v>496.03</v>
       </c>
       <c r="E18" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="F18" t="n">
-        <v>-26.54</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.001\PPO_results.txt</t>
+        <v>4.78</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L18" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="M18" t="n">
+        <v>450.82</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.000\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="D19" t="n">
-        <v>274.08</v>
+        <v>494.56</v>
       </c>
       <c r="E19" t="n">
-        <v>3.09</v>
+        <v>0.39</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.64</v>
+        <v>1.48</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.010\PPO_results.txt</t>
+        <v>3.84</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="L19" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="M19" t="n">
+        <v>290.37</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.001\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D20" t="n">
-        <v>135.23</v>
+        <v>301.17</v>
       </c>
       <c r="E20" t="n">
-        <v>1.63</v>
+        <v>0.26</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.53</v>
+        <v>-28.04</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.100\PPO_results.txt</t>
+        <v>2.87</v>
+      </c>
+      <c r="H20" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="M20" t="n">
+        <v>174.52</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.010\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D21" t="n">
-        <v>495.74</v>
+        <v>491.92</v>
       </c>
       <c r="E21" t="n">
-        <v>0.34</v>
+        <v>0.88</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.15</v>
+        <v>-2.54</v>
       </c>
       <c r="G21" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.000\SAC_results.txt</t>
+        <v>4.09</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L21" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="M21" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.100\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>494.94</v>
+        <v>496.03</v>
       </c>
       <c r="E22" t="n">
-        <v>0.43</v>
+        <v>0.32</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="G22" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.001\SAC_results.txt</t>
+        <v>4.78</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="M22" t="n">
+        <v>450.88</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.001\ddpg_noise_0.000\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="D23" t="n">
-        <v>489.41</v>
+        <v>494.77</v>
       </c>
       <c r="E23" t="n">
-        <v>3.08</v>
+        <v>0.39</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.16</v>
+        <v>1.37</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.010\SAC_results.txt</t>
+        <v>3.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="M23" t="n">
+        <v>296.83</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.001\ddpg_noise_0.001\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D24" t="n">
-        <v>494.28</v>
+        <v>301.23</v>
       </c>
       <c r="E24" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.12</v>
+        <v>-28.04</v>
       </c>
       <c r="G24" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.100\SAC_results.txt</t>
+        <v>2.87</v>
+      </c>
+      <c r="H24" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="M24" t="n">
+        <v>175.89</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.001\ddpg_noise_0.010\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TD3</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D25" t="n">
-        <v>492.78</v>
+        <v>491.73</v>
       </c>
       <c r="E25" t="n">
-        <v>0.65</v>
+        <v>0.87</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.71</v>
+        <v>-2.71</v>
       </c>
       <c r="G25" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.000\TD3_results.txt</t>
+        <v>4.02</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="L25" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="M25" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.001\ddpg_noise_0.100\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TD3</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>489.01</v>
+        <v>496.01</v>
       </c>
       <c r="E26" t="n">
-        <v>2.5</v>
+        <v>0.32</v>
       </c>
       <c r="F26" t="n">
-        <v>5.96</v>
+        <v>0.02</v>
       </c>
       <c r="G26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.001\TD3_results.txt</t>
+        <v>4.78</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="M26" t="n">
+        <v>446.31</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.010\ddpg_noise_0.000\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TD3</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="D27" t="n">
-        <v>493.47</v>
+        <v>494.28</v>
       </c>
       <c r="E27" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="F27" t="n">
-        <v>3.25</v>
+        <v>2.16</v>
       </c>
       <c r="G27" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.010\TD3_results.txt</t>
+        <v>3.62</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="M27" t="n">
+        <v>302.19</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.010\ddpg_noise_0.001\DDPG_results.txt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D28" t="n">
+        <v>300.99</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-27.99</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H28" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I28" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="K28" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="M28" t="n">
+        <v>184.11</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.010\ddpg_noise_0.010\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>491.93</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K29" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="M29" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.010\ddpg_noise_0.100\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>495.32</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L30" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="M30" t="n">
+        <v>414.96</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.100\ddpg_noise_0.000\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>492.83</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="J31" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K31" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="L31" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="M31" t="n">
+        <v>371.57</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.100\ddpg_noise_0.001\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D32" t="n">
+        <v>205.47</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-39.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H32" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="I32" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="J32" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="L32" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="M32" t="n">
+        <v>163.97</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.100\ddpg_noise_0.010\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>486.05</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H33" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K33" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="L33" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="M33" t="n">
+        <v>104.19</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.100\ddpg_noise_0.100\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>465.72</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-20.25</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H34" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="K34" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="L34" t="n">
+        <v>103.57</v>
+      </c>
+      <c r="M34" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.000\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D35" t="n">
+        <v>478.08</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-15.24</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H35" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="I35" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K35" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="L35" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="M35" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.001\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D36" t="n">
+        <v>473.33</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-17.57</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="I36" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K36" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="L36" t="n">
+        <v>90.84</v>
+      </c>
+      <c r="M36" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.010\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>301.27</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-31.39</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H37" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="L37" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="M37" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.100\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F38" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H38" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="I38" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="J38" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.001\dqn_noise_0.000\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F39" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="I39" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="J39" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.001\dqn_noise_0.001\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D40" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F40" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H40" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="I40" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="J40" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.001\dqn_noise_0.010\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H41" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="I41" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="J41" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="K41" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="L41" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.001\dqn_noise_0.100\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>467.85</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-19.13</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H42" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="I42" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K42" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="L42" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="M42" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.010\dqn_noise_0.000\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D43" t="n">
+        <v>478</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-15.42</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H43" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="I43" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="K43" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="L43" t="n">
+        <v>81.20999999999999</v>
+      </c>
+      <c r="M43" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.010\dqn_noise_0.001\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D44" t="n">
+        <v>473.91</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-17.38</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H44" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="I44" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K44" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="M44" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.010\dqn_noise_0.010\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>301.3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-31.34</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="I45" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="K45" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="L45" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="M45" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.010\dqn_noise_0.100\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>471.14</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-18.22</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H46" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="I46" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K46" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="L46" t="n">
+        <v>93.94</v>
+      </c>
+      <c r="M46" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.100\dqn_noise_0.000\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D47" t="n">
+        <v>473.65</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-17.43</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I47" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="K47" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="L47" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="M47" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.100\dqn_noise_0.001\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D48" t="n">
+        <v>476.61</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-16.16</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H48" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="I48" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="K48" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="L48" t="n">
+        <v>83.95999999999999</v>
+      </c>
+      <c r="M48" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.100\dqn_noise_0.010\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>393.27</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-20.87</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H49" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="I49" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="J49" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="K49" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="L49" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="M49" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.100\dqn_noise_0.100\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>305.26</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-27.16</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H50" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I50" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="L50" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="M50" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.000\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D51" t="n">
+        <v>112.03</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-26.54</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H51" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I51" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="J51" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L51" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.001\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D52" t="n">
+        <v>274.08</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-20.64</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="I52" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="K52" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="L52" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="M52" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.010\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>135.23</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-20.53</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="I53" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="J53" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="M53" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.100\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>305.26</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-27.16</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H54" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I54" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="K54" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="L54" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="M54" t="n">
+        <v>141.66</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.001\ppo_noise_0.000\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D55" t="n">
+        <v>112.03</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-26.55</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H55" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="I55" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="J55" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="K55" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="L55" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.001\ppo_noise_0.001\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D56" t="n">
+        <v>274.09</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-20.68</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="I56" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="K56" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="L56" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="M56" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.001\ppo_noise_0.010\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>135.23</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>61.52</v>
+      </c>
+      <c r="I57" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="J57" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K57" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="L57" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="M57" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.001\ppo_noise_0.100\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>305.42</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-27.29</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H58" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="I58" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="K58" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="L58" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="M58" t="n">
+        <v>143.55</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.010\ppo_noise_0.000\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D59" t="n">
+        <v>112.03</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-26.62</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="I59" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="J59" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="K59" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="L59" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.010\ppo_noise_0.001\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D60" t="n">
+        <v>273.47</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-20.57</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="I60" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="J60" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>35</v>
+      </c>
+      <c r="L60" t="n">
+        <v>81.63</v>
+      </c>
+      <c r="M60" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.010\ppo_noise_0.010\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>135.27</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-21.27</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="I61" t="n">
+        <v>62.39</v>
+      </c>
+      <c r="J61" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K61" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="L61" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="M61" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.010\ppo_noise_0.100\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>305.83</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H62" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="I62" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="J62" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="K62" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="L62" t="n">
+        <v>26</v>
+      </c>
+      <c r="M62" t="n">
+        <v>139.17</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.100\ppo_noise_0.000\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D63" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-34.98</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H63" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="I63" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J63" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="K63" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="L63" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.100\ppo_noise_0.001\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D64" t="n">
+        <v>138.64</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-19.62</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H64" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="I64" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="J64" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="K64" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="L64" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="M64" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.100\ppo_noise_0.010\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>108.99</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-18.54</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H65" t="n">
+        <v>63.62</v>
+      </c>
+      <c r="I65" t="n">
+        <v>65.13</v>
+      </c>
+      <c r="J65" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="K65" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="L65" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="M65" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.100\ppo_noise_0.100\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>495.74</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L66" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="M66" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.000\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D67" t="n">
+        <v>494.94</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L67" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="M67" t="n">
+        <v>182.68</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.001\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D68" t="n">
+        <v>489.41</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-8.16</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="I68" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K68" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="L68" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="M68" t="n">
+        <v>336.48</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.010\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>494.28</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L69" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="M69" t="n">
+        <v>229.07</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.100\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>495.74</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L70" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="M70" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.001\sac_noise_0.000\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D71" t="n">
+        <v>494.94</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L71" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="M71" t="n">
+        <v>187.69</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.001\sac_noise_0.001\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D72" t="n">
+        <v>489.43</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H72" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="I72" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K72" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="L72" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="M72" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.001\sac_noise_0.010\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>494.29</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L73" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="M73" t="n">
+        <v>234.52</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.001\sac_noise_0.100\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>495.74</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L74" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M74" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.010\sac_noise_0.000\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D75" t="n">
+        <v>494.94</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L75" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.010\sac_noise_0.001\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D76" t="n">
+        <v>489.46</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-8.06</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="I76" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K76" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="L76" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="M76" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.010\sac_noise_0.010\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>494.26</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L77" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="M77" t="n">
+        <v>197.31</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.010\sac_noise_0.100\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>495.33</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I78" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="J78" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="K78" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="L78" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="M78" t="n">
+        <v>280.26</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.100\sac_noise_0.000\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D79" t="n">
+        <v>494.32</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H79" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="I79" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J79" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="L79" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="M79" t="n">
+        <v>245.74</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.100\sac_noise_0.001\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D80" t="n">
+        <v>486.66</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-10.24</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H80" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="I80" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="J80" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K80" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="L80" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="M80" t="n">
+        <v>282.13</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.100\sac_noise_0.010\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>494.13</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I81" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="J81" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="K81" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="L81" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="M81" t="n">
+        <v>256.91</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.100\sac_noise_0.100\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>TD3</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>492.78</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="G82" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K82" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="L82" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="M82" t="n">
+        <v>227.81</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.000\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D83" t="n">
+        <v>489.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H83" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="I83" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K83" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="L83" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="M83" t="n">
+        <v>423.39</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.001\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D84" t="n">
+        <v>493.47</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G84" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="L84" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="M84" t="n">
+        <v>120.67</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.010\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="n">
         <v>0.1</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D85" t="n">
         <v>489.64</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E85" t="n">
         <v>0.8</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F85" t="n">
         <v>3.21</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G85" t="n">
         <v>2.96</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H85" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I85" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J85" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K85" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="L85" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="M85" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.100\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>492.85</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K86" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="L86" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="M86" t="n">
+        <v>228.52</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.001\td3_noise_0.000\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D87" t="n">
+        <v>490.12</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H87" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="I87" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K87" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="L87" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="M87" t="n">
+        <v>433.17</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.001\td3_noise_0.001\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D88" t="n">
+        <v>493.47</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G88" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="L88" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="M88" t="n">
+        <v>120.63</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.001\td3_noise_0.010\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>489.3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I89" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="J89" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="K89" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="L89" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="M89" t="n">
+        <v>88.53</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.001\td3_noise_0.100\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>493.22</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="L90" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="M90" t="n">
+        <v>229.86</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.010\td3_noise_0.000\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D91" t="n">
+        <v>487.63</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H91" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="I91" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="J91" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K91" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="L91" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="M91" t="n">
+        <v>413.41</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.010\td3_noise_0.001\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D92" t="n">
+        <v>493.34</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F92" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G92" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H92" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="I92" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K92" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="L92" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="M92" t="n">
+        <v>136.73</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.010\td3_noise_0.010\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>489.25</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H93" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I93" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="J93" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="K93" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="L93" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="M93" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.010\td3_noise_0.100\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>494.36</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H94" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I94" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="J94" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="K94" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="L94" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="M94" t="n">
+        <v>296.73</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.100\td3_noise_0.000\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D95" t="n">
+        <v>489.9</v>
+      </c>
+      <c r="E95" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H95" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="I95" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="J95" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="K95" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L95" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="M95" t="n">
+        <v>420.44</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.100\td3_noise_0.001\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D96" t="n">
+        <v>490.99</v>
+      </c>
+      <c r="E96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I96" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="K96" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="L96" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>175.28</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.100\td3_noise_0.010\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>490.46</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H97" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I97" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="J97" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K97" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L97" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="M97" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.100\td3_noise_0.100\TD3_results.txt</t>
         </is>
       </c>
     </row>
@@ -1307,56 +5141,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>env_noise</t>
+          <t>EnvNoise</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>run_noise</t>
+          <t>RunNoise</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_reward</t>
+          <t>Mean Reward</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_stabilisation_time_s</t>
+          <t>Mean Stabilisation Time</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_steady_state_offset_deg</t>
+          <t>Mean Steady-state offset</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_total_stable_time_s</t>
+          <t>Mean Total Stable Time</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State MAE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State RMSE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Oscillation (σ)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mean |Overshoot/Undershoot|</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mean IAE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Control Energy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>results_path</t>
         </is>
@@ -1386,7 +5256,25 @@
       <c r="G2" t="n">
         <v>4.67</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>plots\A2C\a2c_env_noise_0.000\a2c_noise_0.000\A2C_results.txt</t>
         </is>
@@ -1416,7 +5304,25 @@
       <c r="G3" t="n">
         <v>4.61</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="L3" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="M3" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>plots\A2C\a2c_env_noise_0.000\a2c_noise_0.001\A2C_results.txt</t>
         </is>
@@ -1446,7 +5352,25 @@
       <c r="G4" t="n">
         <v>4.69</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>plots\A2C\a2c_env_noise_0.000\a2c_noise_0.010\A2C_results.txt</t>
         </is>
@@ -1476,7 +5400,25 @@
       <c r="G5" t="n">
         <v>2.33</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="M5" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>plots\A2C\a2c_env_noise_0.000\a2c_noise_0.100\A2C_results.txt</t>
         </is>
@@ -1495,20 +5437,38 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>492.92</v>
+        <v>494.88</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3</v>
+        <v>0.43</v>
       </c>
       <c r="F6" t="n">
-        <v>6.21</v>
+        <v>3.84</v>
       </c>
       <c r="G6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>plots\A2C\a2c_env_noise_0.001\a2c\A2C_results.txt</t>
+        <v>4.67</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L6" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.001\a2c_noise_0.000\A2C_results.txt</t>
         </is>
       </c>
     </row>
@@ -1519,26 +5479,44 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D7" t="n">
-        <v>492.92</v>
+        <v>495.49</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3</v>
+        <v>0.49</v>
       </c>
       <c r="F7" t="n">
-        <v>6.21</v>
+        <v>-1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>plots\A2C\a2c_env_noise_0.010\a2c\A2C_results.txt</t>
+        <v>4.61</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="L7" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="M7" t="n">
+        <v>320.13</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.001\a2c_noise_0.001\A2C_results.txt</t>
         </is>
       </c>
     </row>
@@ -1549,26 +5527,476 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>495.85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.001\a2c_noise_0.010\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.1</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>492.43</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D9" t="n">
+        <v>305.31</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-27.02</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="L9" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="M9" t="n">
+        <v>70.31</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.001\a2c_noise_0.100\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>494.81</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="L10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.010\a2c_noise_0.000\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>495.49</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L11" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="M11" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.010\a2c_noise_0.001\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D12" t="n">
+        <v>495.86</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="M12" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.010\a2c_noise_0.010\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>305.23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-26.78</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H13" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="I13" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="K13" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.010\a2c_noise_0.100\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>493.58</v>
+      </c>
+      <c r="E14" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>plots\A2C\a2c_env_noise_0.100\a2c\A2C_results.txt</t>
+      <c r="F14" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="L14" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="M14" t="n">
+        <v>106.31</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.100\a2c_noise_0.000\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>495.24</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.100\a2c_noise_0.001\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" t="n">
+        <v>495.59</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.100\a2c_noise_0.010\A2C_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>305.19</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-29.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H17" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="I17" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="K17" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="L17" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.03</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>plots\A2C\a2c_env_noise_0.100\a2c_noise_0.100\A2C_results.txt</t>
         </is>
       </c>
     </row>
@@ -1583,56 +6011,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>env_noise</t>
+          <t>EnvNoise</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>run_noise</t>
+          <t>RunNoise</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_reward</t>
+          <t>Mean Reward</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_stabilisation_time_s</t>
+          <t>Mean Stabilisation Time</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_steady_state_offset_deg</t>
+          <t>Mean Steady-state offset</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_total_stable_time_s</t>
+          <t>Mean Total Stable Time</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State MAE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State RMSE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Oscillation (σ)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mean |Overshoot/Undershoot|</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mean IAE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Control Energy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>results_path</t>
         </is>
@@ -1662,7 +6126,25 @@
       <c r="G2" t="n">
         <v>4.78</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="M2" t="n">
+        <v>450.82</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.000\DDPG_results.txt</t>
         </is>
@@ -1692,7 +6174,25 @@
       <c r="G3" t="n">
         <v>3.84</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="L3" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="M3" t="n">
+        <v>290.37</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.001\DDPG_results.txt</t>
         </is>
@@ -1722,7 +6222,25 @@
       <c r="G4" t="n">
         <v>2.87</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I4" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="M4" t="n">
+        <v>174.52</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.010\DDPG_results.txt</t>
         </is>
@@ -1752,9 +6270,603 @@
       <c r="G5" t="n">
         <v>4.09</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="M5" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>plots\DDPG\ddpg_env_noise_0.000\ddpg_noise_0.100\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>496.03</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>450.88</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.001\ddpg_noise_0.000\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>494.77</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="L7" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="M7" t="n">
+        <v>296.83</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.001\ddpg_noise_0.001\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>301.23</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-28.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H8" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="I8" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="M8" t="n">
+        <v>175.89</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.001\ddpg_noise_0.010\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>491.73</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="L9" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.001\ddpg_noise_0.100\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>496.01</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>446.31</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.010\ddpg_noise_0.000\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>494.28</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="L11" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>302.19</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.010\ddpg_noise_0.001\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D12" t="n">
+        <v>300.99</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-27.99</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H12" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I12" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="M12" t="n">
+        <v>184.11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.010\ddpg_noise_0.010\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>491.93</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.010\ddpg_noise_0.100\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>495.32</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L14" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="M14" t="n">
+        <v>414.96</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.100\ddpg_noise_0.000\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>492.83</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="L15" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="M15" t="n">
+        <v>371.57</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.100\ddpg_noise_0.001\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" t="n">
+        <v>205.47</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-39.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H16" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="I16" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="K16" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="M16" t="n">
+        <v>163.97</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.100\ddpg_noise_0.010\DDPG_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DDPG</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>486.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="L17" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="M17" t="n">
+        <v>104.19</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>plots\DDPG\ddpg_env_noise_0.100\ddpg_noise_0.100\DDPG_results.txt</t>
         </is>
       </c>
     </row>
@@ -1769,56 +6881,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>env_noise</t>
+          <t>EnvNoise</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>run_noise</t>
+          <t>RunNoise</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_reward</t>
+          <t>Mean Reward</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_stabilisation_time_s</t>
+          <t>Mean Stabilisation Time</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_steady_state_offset_deg</t>
+          <t>Mean Steady-state offset</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_total_stable_time_s</t>
+          <t>Mean Total Stable Time</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State MAE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State RMSE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Oscillation (σ)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mean |Overshoot/Undershoot|</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mean IAE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Control Energy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>results_path</t>
         </is>
@@ -1848,7 +6996,25 @@
       <c r="G2" t="n">
         <v>0.08</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="L2" t="n">
+        <v>103.57</v>
+      </c>
+      <c r="M2" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.000\DQN_results.txt</t>
         </is>
@@ -1878,7 +7044,25 @@
       <c r="G3" t="n">
         <v>0.08</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="I3" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="L3" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.001\DQN_results.txt</t>
         </is>
@@ -1908,7 +7092,25 @@
       <c r="G4" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K4" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="L4" t="n">
+        <v>90.84</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.010\DQN_results.txt</t>
         </is>
@@ -1938,9 +7140,603 @@
       <c r="G5" t="n">
         <v>0.28</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>plots\DQN\dqn_env_noise_0.000\dqn_noise_0.100\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H6" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="I6" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="J6" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.001\dqn_noise_0.000\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F7" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H7" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.001\dqn_noise_0.001\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="I8" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.001\dqn_noise_0.010\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H9" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="I9" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.001\dqn_noise_0.100\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>467.85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-19.13</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K10" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="L10" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="M10" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.010\dqn_noise_0.000\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>478</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-15.42</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="K11" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="L11" t="n">
+        <v>81.20999999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.010\dqn_noise_0.001\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D12" t="n">
+        <v>473.91</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-17.38</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H12" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="I12" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K12" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.010\dqn_noise_0.010\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>301.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-31.34</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="I13" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="K13" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.010\dqn_noise_0.100\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>471.14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-18.22</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H14" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="I14" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="L14" t="n">
+        <v>93.94</v>
+      </c>
+      <c r="M14" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.100\dqn_noise_0.000\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>473.65</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-17.43</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I15" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="L15" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="M15" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.100\dqn_noise_0.001\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" t="n">
+        <v>476.61</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-16.16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="I16" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>83.95999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.100\dqn_noise_0.010\DQN_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DQN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>393.27</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-20.87</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H17" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="L17" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="M17" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>plots\DQN\dqn_env_noise_0.100\dqn_noise_0.100\DQN_results.txt</t>
         </is>
       </c>
     </row>
@@ -1955,56 +7751,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>env_noise</t>
+          <t>EnvNoise</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>run_noise</t>
+          <t>RunNoise</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_reward</t>
+          <t>Mean Reward</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_stabilisation_time_s</t>
+          <t>Mean Stabilisation Time</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_steady_state_offset_deg</t>
+          <t>Mean Steady-state offset</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_total_stable_time_s</t>
+          <t>Mean Total Stable Time</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State MAE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State RMSE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Oscillation (σ)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mean |Overshoot/Undershoot|</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mean IAE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Control Energy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>results_path</t>
         </is>
@@ -2034,7 +7866,25 @@
       <c r="G2" t="n">
         <v>2.56</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I2" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="L2" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="M2" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.000\PPO_results.txt</t>
         </is>
@@ -2064,7 +7914,25 @@
       <c r="G3" t="n">
         <v>0.95</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I3" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.001\PPO_results.txt</t>
         </is>
@@ -2094,7 +7962,25 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="I4" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="L4" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="M4" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.010\PPO_results.txt</t>
         </is>
@@ -2124,9 +8010,603 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="M5" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>plots\PPO\ppo_env_noise_0.000\ppo_noise_0.100\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>305.26</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-27.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H6" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="K6" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="L6" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="M6" t="n">
+        <v>141.66</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.001\ppo_noise_0.000\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>112.03</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-26.55</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="I7" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.001\ppo_noise_0.001\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>274.09</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-20.68</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.001\ppo_noise_0.010\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>135.23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>61.52</v>
+      </c>
+      <c r="I9" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="L9" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.001\ppo_noise_0.100\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>305.42</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-27.29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H10" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="I10" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="K10" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="L10" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="M10" t="n">
+        <v>143.55</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.010\ppo_noise_0.000\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>112.03</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-26.62</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="I11" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.010\ppo_noise_0.001\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D12" t="n">
+        <v>273.47</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-20.57</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="I12" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>35</v>
+      </c>
+      <c r="L12" t="n">
+        <v>81.63</v>
+      </c>
+      <c r="M12" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.010\ppo_noise_0.010\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>135.27</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-21.27</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="I13" t="n">
+        <v>62.39</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K13" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="L13" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.010\ppo_noise_0.100\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>305.83</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H14" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="I14" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="L14" t="n">
+        <v>26</v>
+      </c>
+      <c r="M14" t="n">
+        <v>139.17</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.100\ppo_noise_0.000\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-34.98</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H15" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="I15" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="K15" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="L15" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.100\ppo_noise_0.001\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" t="n">
+        <v>138.64</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-19.62</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H16" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="J16" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="K16" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="L16" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="M16" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.100\ppo_noise_0.010\PPO_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>108.99</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-18.54</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H17" t="n">
+        <v>63.62</v>
+      </c>
+      <c r="I17" t="n">
+        <v>65.13</v>
+      </c>
+      <c r="J17" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="K17" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="L17" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>plots\PPO\ppo_env_noise_0.100\ppo_noise_0.100\PPO_results.txt</t>
         </is>
       </c>
     </row>
@@ -2141,56 +8621,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>env_noise</t>
+          <t>EnvNoise</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>run_noise</t>
+          <t>RunNoise</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_reward</t>
+          <t>Mean Reward</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_stabilisation_time_s</t>
+          <t>Mean Stabilisation Time</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_steady_state_offset_deg</t>
+          <t>Mean Steady-state offset</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_total_stable_time_s</t>
+          <t>Mean Total Stable Time</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State MAE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State RMSE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Oscillation (σ)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mean |Overshoot/Undershoot|</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mean IAE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Control Energy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>results_path</t>
         </is>
@@ -2220,7 +8736,25 @@
       <c r="G2" t="n">
         <v>4.76</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.000\SAC_results.txt</t>
         </is>
@@ -2250,7 +8784,25 @@
       <c r="G3" t="n">
         <v>4.67</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="M3" t="n">
+        <v>182.68</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.001\SAC_results.txt</t>
         </is>
@@ -2280,7 +8832,25 @@
       <c r="G4" t="n">
         <v>0.1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="L4" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="M4" t="n">
+        <v>336.48</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.010\SAC_results.txt</t>
         </is>
@@ -2310,9 +8880,603 @@
       <c r="G5" t="n">
         <v>4.53</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>229.07</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>plots\SAC\sac_env_noise_0.000\sac_noise_0.100\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>495.74</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.001\sac_noise_0.000\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>494.94</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="M7" t="n">
+        <v>187.69</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.001\sac_noise_0.001\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>489.43</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K8" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="L8" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="M8" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.001\sac_noise_0.010\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>494.29</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="M9" t="n">
+        <v>234.52</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.001\sac_noise_0.100\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>495.74</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M10" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.010\sac_noise_0.000\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>494.94</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.010\sac_noise_0.001\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D12" t="n">
+        <v>489.46</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-8.06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K12" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="L12" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="M12" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.010\sac_noise_0.010\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>494.26</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="M13" t="n">
+        <v>197.31</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.010\sac_noise_0.100\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>495.33</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="L14" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>280.26</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.100\sac_noise_0.000\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>494.32</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="M15" t="n">
+        <v>245.74</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.100\sac_noise_0.001\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" t="n">
+        <v>486.66</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-10.24</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K16" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="L16" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>282.13</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.100\sac_noise_0.010\SAC_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>494.13</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="M17" t="n">
+        <v>256.91</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>plots\SAC\sac_env_noise_0.100\sac_noise_0.100\SAC_results.txt</t>
         </is>
       </c>
     </row>
@@ -2327,56 +9491,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>env_noise</t>
+          <t>EnvNoise</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>run_noise</t>
+          <t>RunNoise</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_reward</t>
+          <t>Mean Reward</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_stabilisation_time_s</t>
+          <t>Mean Stabilisation Time</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_steady_state_offset_deg</t>
+          <t>Mean Steady-state offset</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_total_stable_time_s</t>
+          <t>Mean Total Stable Time</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State MAE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Steady-State RMSE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Oscillation (σ)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mean |Overshoot/Undershoot|</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mean IAE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Control Energy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>results_path</t>
         </is>
@@ -2406,7 +9606,25 @@
       <c r="G2" t="n">
         <v>4.47</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="L2" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="M2" t="n">
+        <v>227.81</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.000\TD3_results.txt</t>
         </is>
@@ -2436,7 +9654,25 @@
       <c r="G3" t="n">
         <v>1.95</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="L3" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="M3" t="n">
+        <v>423.39</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.001\TD3_results.txt</t>
         </is>
@@ -2466,7 +9702,25 @@
       <c r="G4" t="n">
         <v>4.52</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="M4" t="n">
+        <v>120.67</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.010\TD3_results.txt</t>
         </is>
@@ -2496,9 +9750,603 @@
       <c r="G5" t="n">
         <v>2.96</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="L5" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="M5" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>plots\TD3\td3_env_noise_0.000\td3_noise_0.100\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>492.85</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K6" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="L6" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="M6" t="n">
+        <v>228.52</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.001\td3_noise_0.000\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>490.12</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="L7" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="M7" t="n">
+        <v>433.17</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.001\td3_noise_0.001\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>493.47</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>120.63</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.001\td3_noise_0.010\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>489.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="L9" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="M9" t="n">
+        <v>88.53</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.001\td3_noise_0.100\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>493.22</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="M10" t="n">
+        <v>229.86</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.010\td3_noise_0.000\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>487.63</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="L11" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="M11" t="n">
+        <v>413.41</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.010\td3_noise_0.001\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D12" t="n">
+        <v>493.34</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="L12" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="M12" t="n">
+        <v>136.73</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.010\td3_noise_0.010\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>489.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="L13" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="M13" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.010\td3_noise_0.100\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>494.36</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="L14" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="M14" t="n">
+        <v>296.73</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.100\td3_noise_0.000\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>489.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>420.44</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.100\td3_noise_0.001\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" t="n">
+        <v>490.99</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="L16" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>175.28</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.100\td3_noise_0.010\TD3_results.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>490.46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="M17" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>plots\TD3\td3_env_noise_0.100\td3_noise_0.100\TD3_results.txt</t>
         </is>
       </c>
     </row>
